--- a/src/test/resources/testData/ElectricCars.xlsx
+++ b/src/test/resources/testData/ElectricCars.xlsx
@@ -104,15 +104,6 @@
     <t>EMI : ₹41,571</t>
   </si>
   <si>
-    <t>Tata Tiago EV</t>
-  </si>
-  <si>
-    <t>₹ 7.99 Lakh</t>
-  </si>
-  <si>
-    <t>EMI : ₹15,456</t>
-  </si>
-  <si>
     <t>Kia EV6</t>
   </si>
   <si>
@@ -131,6 +122,15 @@
     <t>EMI : ₹42,345</t>
   </si>
   <si>
+    <t>VinFast VF MPV 7</t>
+  </si>
+  <si>
+    <t>₹ 24.49 Lakh</t>
+  </si>
+  <si>
+    <t>EMI : ₹47,375</t>
+  </si>
+  <si>
     <t>Vayve Mobility Eva</t>
   </si>
   <si>
@@ -140,13 +140,22 @@
     <t>EMI : ₹6,287</t>
   </si>
   <si>
-    <t>VinFast VF MPV 7</t>
-  </si>
-  <si>
-    <t>₹ 24.49 Lakh</t>
-  </si>
-  <si>
-    <t>EMI : ₹47,375</t>
+    <t>MG ZS EV</t>
+  </si>
+  <si>
+    <t>₹ 17.99 Lakh</t>
+  </si>
+  <si>
+    <t>EMI : ₹34,801</t>
+  </si>
+  <si>
+    <t>Tata Curvv EV</t>
+  </si>
+  <si>
+    <t>₹ 17.49 Lakh</t>
+  </si>
+  <si>
+    <t>EMI : ₹33,834</t>
   </si>
   <si>
     <t>VinFast VF6</t>
@@ -158,24 +167,6 @@
     <t>EMI : ₹33,447</t>
   </si>
   <si>
-    <t>Tata Curvv EV</t>
-  </si>
-  <si>
-    <t>₹ 17.49 Lakh</t>
-  </si>
-  <si>
-    <t>EMI : ₹33,834</t>
-  </si>
-  <si>
-    <t>MG ZS EV</t>
-  </si>
-  <si>
-    <t>₹ 17.99 Lakh</t>
-  </si>
-  <si>
-    <t>EMI : ₹34,801</t>
-  </si>
-  <si>
     <t>Hyundai Creta Electric</t>
   </si>
   <si>
@@ -201,6 +192,15 @@
   </si>
   <si>
     <t>EMI : ₹1.16 Lakh</t>
+  </si>
+  <si>
+    <t>BYD Atto 3</t>
+  </si>
+  <si>
+    <t>₹ 24.99 Lakh</t>
+  </si>
+  <si>
+    <t>EMI : ₹48,342</t>
   </si>
 </sst>
 </file>

--- a/src/test/resources/testData/ElectricCars.xlsx
+++ b/src/test/resources/testData/ElectricCars.xlsx
@@ -50,15 +50,6 @@
     <t>EMI : ₹18,745</t>
   </si>
   <si>
-    <t>MG Windsor EV</t>
-  </si>
-  <si>
-    <t>₹ 14.00 Lakh</t>
-  </si>
-  <si>
-    <t>EMI : ₹27,078</t>
-  </si>
-  <si>
     <t>Mahindra XEV 9e</t>
   </si>
   <si>
@@ -167,6 +158,15 @@
     <t>EMI : ₹33,447</t>
   </si>
   <si>
+    <t>BMW iX1</t>
+  </si>
+  <si>
+    <t>₹ 50.90 Lakh</t>
+  </si>
+  <si>
+    <t>EMI : ₹98,464</t>
+  </si>
+  <si>
     <t>Hyundai Creta Electric</t>
   </si>
   <si>
@@ -176,15 +176,6 @@
     <t>EMI : ₹34,863</t>
   </si>
   <si>
-    <t>BMW iX1</t>
-  </si>
-  <si>
-    <t>₹ 50.90 Lakh</t>
-  </si>
-  <si>
-    <t>EMI : ₹98,464</t>
-  </si>
-  <si>
     <t>Tesla Model Y</t>
   </si>
   <si>
@@ -201,6 +192,15 @@
   </si>
   <si>
     <t>EMI : ₹48,342</t>
+  </si>
+  <si>
+    <t>BMW i7</t>
+  </si>
+  <si>
+    <t>₹ 2.05 Crore</t>
+  </si>
+  <si>
+    <t>EMI : ₹3.97 Lakh</t>
   </si>
 </sst>
 </file>

--- a/src/test/resources/testData/ElectricCars.xlsx
+++ b/src/test/resources/testData/ElectricCars.xlsx
@@ -59,6 +59,15 @@
     <t>EMI : ₹42,364</t>
   </si>
   <si>
+    <t>MG Cyberster</t>
+  </si>
+  <si>
+    <t>₹ 75.00 Lakh</t>
+  </si>
+  <si>
+    <t>EMI : ₹1.45 Lakh</t>
+  </si>
+  <si>
     <t>MG Comet EV</t>
   </si>
   <si>
@@ -68,15 +77,6 @@
     <t>EMI : ₹14,505</t>
   </si>
   <si>
-    <t>MG Cyberster</t>
-  </si>
-  <si>
-    <t>₹ 75.00 Lakh</t>
-  </si>
-  <si>
-    <t>EMI : ₹1.45 Lakh</t>
-  </si>
-  <si>
     <t>Tata Nexon EV</t>
   </si>
   <si>
@@ -131,6 +131,15 @@
     <t>EMI : ₹6,287</t>
   </si>
   <si>
+    <t>Tata Curvv EV</t>
+  </si>
+  <si>
+    <t>₹ 17.49 Lakh</t>
+  </si>
+  <si>
+    <t>EMI : ₹33,834</t>
+  </si>
+  <si>
     <t>MG ZS EV</t>
   </si>
   <si>
@@ -138,15 +147,6 @@
   </si>
   <si>
     <t>EMI : ₹34,801</t>
-  </si>
-  <si>
-    <t>Tata Curvv EV</t>
-  </si>
-  <si>
-    <t>₹ 17.49 Lakh</t>
-  </si>
-  <si>
-    <t>EMI : ₹33,834</t>
   </si>
   <si>
     <t>VinFast VF6</t>

--- a/src/test/resources/testData/ElectricCars.xlsx
+++ b/src/test/resources/testData/ElectricCars.xlsx
@@ -50,15 +50,6 @@
     <t>EMI : ₹18,745</t>
   </si>
   <si>
-    <t>MG Windsor EV</t>
-  </si>
-  <si>
-    <t>₹ 14.00 Lakh</t>
-  </si>
-  <si>
-    <t>EMI : ₹27,078</t>
-  </si>
-  <si>
     <t>Mahindra XEV 9e</t>
   </si>
   <si>
@@ -167,6 +158,15 @@
     <t>EMI : ₹33,447</t>
   </si>
   <si>
+    <t>BMW iX1</t>
+  </si>
+  <si>
+    <t>₹ 50.90 Lakh</t>
+  </si>
+  <si>
+    <t>EMI : ₹98,464</t>
+  </si>
+  <si>
     <t>Hyundai Creta Electric</t>
   </si>
   <si>
@@ -176,15 +176,6 @@
     <t>EMI : ₹34,863</t>
   </si>
   <si>
-    <t>BMW iX1</t>
-  </si>
-  <si>
-    <t>₹ 50.90 Lakh</t>
-  </si>
-  <si>
-    <t>EMI : ₹98,464</t>
-  </si>
-  <si>
     <t>Tesla Model Y</t>
   </si>
   <si>
@@ -201,6 +192,15 @@
   </si>
   <si>
     <t>EMI : ₹48,342</t>
+  </si>
+  <si>
+    <t>Mercedes-Benz CLA Electric</t>
+  </si>
+  <si>
+    <t>₹ 55.00 Lakh</t>
+  </si>
+  <si>
+    <t>EMI : ₹1.06 Lakh</t>
   </si>
 </sst>
 </file>

--- a/src/test/resources/testData/ElectricCars.xlsx
+++ b/src/test/resources/testData/ElectricCars.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <si>
     <t>Car Name</t>
   </si>
@@ -26,91 +26,181 @@
     <t>Maruti Suzuki e Vitara</t>
   </si>
   <si>
-    <t>Rs. 15.99 Lakh</t>
-  </si>
-  <si>
-    <t>EMI : Rs. 30,932</t>
+    <t>₹ 15.99 Lakh</t>
+  </si>
+  <si>
+    <t>EMI : ₹30,932</t>
   </si>
   <si>
     <t>Mahindra BE 6</t>
   </si>
   <si>
-    <t>Rs. 18.90 Lakh</t>
-  </si>
-  <si>
-    <t>EMI : Rs. 36,561</t>
+    <t>₹ 18.90 Lakh</t>
+  </si>
+  <si>
+    <t>EMI : ₹36,561</t>
   </si>
   <si>
     <t>Tata Punch EV</t>
   </si>
   <si>
-    <t>Rs. 9.69 Lakh</t>
-  </si>
-  <si>
-    <t>EMI : Rs. 18,745</t>
+    <t>₹ 9.69 Lakh</t>
+  </si>
+  <si>
+    <t>EMI : ₹18,745</t>
+  </si>
+  <si>
+    <t>MG Windsor EV</t>
+  </si>
+  <si>
+    <t>₹ 14.00 Lakh</t>
+  </si>
+  <si>
+    <t>EMI : ₹27,078</t>
   </si>
   <si>
     <t>Mahindra XEV 9e</t>
   </si>
   <si>
-    <t>Rs. 21.90 Lakh</t>
-  </si>
-  <si>
-    <t>EMI : Rs. 42,364</t>
+    <t>₹ 21.90 Lakh</t>
+  </si>
+  <si>
+    <t>EMI : ₹42,364</t>
   </si>
   <si>
     <t>MG Cyberster</t>
   </si>
   <si>
-    <t>Rs. 75.00 Lakh</t>
-  </si>
-  <si>
-    <t>EMI : Rs. 1.45 Lakh</t>
+    <t>₹ 75.00 Lakh</t>
+  </si>
+  <si>
+    <t>EMI : ₹1.45 Lakh</t>
   </si>
   <si>
     <t>MG Comet EV</t>
   </si>
   <si>
-    <t>Rs. 7.50 Lakh</t>
-  </si>
-  <si>
-    <t>EMI : Rs. 14,505</t>
+    <t>₹ 7.50 Lakh</t>
+  </si>
+  <si>
+    <t>EMI : ₹14,505</t>
   </si>
   <si>
     <t>Tata Nexon EV</t>
   </si>
   <si>
-    <t>Rs. 12.49 Lakh</t>
-  </si>
-  <si>
-    <t>EMI : Rs. 24,161</t>
+    <t>₹ 12.49 Lakh</t>
+  </si>
+  <si>
+    <t>EMI : ₹24,161</t>
   </si>
   <si>
     <t>Tata Harrier EV</t>
   </si>
   <si>
-    <t>Rs. 21.49 Lakh</t>
-  </si>
-  <si>
-    <t>EMI : Rs. 41,571</t>
+    <t>₹ 21.49 Lakh</t>
+  </si>
+  <si>
+    <t>EMI : ₹41,571</t>
+  </si>
+  <si>
+    <t>Tata Tiago EV</t>
+  </si>
+  <si>
+    <t>₹ 7.99 Lakh</t>
+  </si>
+  <si>
+    <t>EMI : ₹15,456</t>
   </si>
   <si>
     <t>Kia EV6</t>
   </si>
   <si>
-    <t>Rs. 65.97 Lakh</t>
-  </si>
-  <si>
-    <t>EMI : Rs. 1.28 Lakh</t>
+    <t>₹ 65.97 Lakh</t>
+  </si>
+  <si>
+    <t>EMI : ₹1.28 Lakh</t>
   </si>
   <si>
     <t>VinFast VF7</t>
   </si>
   <si>
-    <t>Rs. 21.89 Lakh</t>
-  </si>
-  <si>
-    <t>EMI : Rs. 42,345</t>
+    <t>₹ 21.89 Lakh</t>
+  </si>
+  <si>
+    <t>EMI : ₹42,345</t>
+  </si>
+  <si>
+    <t>Vayve Mobility Eva</t>
+  </si>
+  <si>
+    <t>₹ 3.25 Lakh</t>
+  </si>
+  <si>
+    <t>EMI : ₹6,287</t>
+  </si>
+  <si>
+    <t>Tata Curvv EV</t>
+  </si>
+  <si>
+    <t>₹ 16.99 Lakh</t>
+  </si>
+  <si>
+    <t>EMI : ₹32,866</t>
+  </si>
+  <si>
+    <t>MG ZS EV</t>
+  </si>
+  <si>
+    <t>₹ 17.99 Lakh</t>
+  </si>
+  <si>
+    <t>EMI : ₹34,801</t>
+  </si>
+  <si>
+    <t>VinFast VF MPV 7</t>
+  </si>
+  <si>
+    <t>₹ 24.49 Lakh</t>
+  </si>
+  <si>
+    <t>EMI : ₹47,375</t>
+  </si>
+  <si>
+    <t>BMW iX1</t>
+  </si>
+  <si>
+    <t>₹ 50.90 Lakh</t>
+  </si>
+  <si>
+    <t>EMI : ₹98,464</t>
+  </si>
+  <si>
+    <t>VinFast VF6</t>
+  </si>
+  <si>
+    <t>₹ 17.29 Lakh</t>
+  </si>
+  <si>
+    <t>EMI : ₹33,447</t>
+  </si>
+  <si>
+    <t>Hyundai Creta Electric</t>
+  </si>
+  <si>
+    <t>₹ 18.02 Lakh</t>
+  </si>
+  <si>
+    <t>EMI : ₹34,863</t>
+  </si>
+  <si>
+    <t>Tesla Model Y</t>
+  </si>
+  <si>
+    <t>₹ 59.89 Lakh</t>
+  </si>
+  <si>
+    <t>EMI : ₹1.16 Lakh</t>
   </si>
 </sst>
 </file>
@@ -155,7 +245,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -279,6 +369,116 @@
         <v>32</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>62</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
